--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/pre LAM_HRM-2031-0172/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.35667</v>
+        <v>17.30155</v>
       </c>
       <c r="D2" t="n">
-        <v>16.83854</v>
+        <v>16.62508</v>
       </c>
       <c r="E2" t="n">
-        <v>16.96771</v>
+        <v>17.17475</v>
       </c>
       <c r="F2" t="n">
-        <v>43.72044</v>
+        <v>41.82505</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05122</v>
+        <v>0.05151</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8854</v>
+        <v>1.83898</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.04414</v>
+        <v>17.06424</v>
       </c>
       <c r="D3" t="n">
-        <v>16.50578</v>
+        <v>16.72437</v>
       </c>
       <c r="E3" t="n">
-        <v>17.12384</v>
+        <v>16.74634</v>
       </c>
       <c r="F3" t="n">
-        <v>43.25206</v>
+        <v>42.13948</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05139</v>
+        <v>0.052</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86141</v>
+        <v>1.87055</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.10072</v>
+        <v>17.03751</v>
       </c>
       <c r="D4" t="n">
-        <v>16.8555</v>
+        <v>16.60556</v>
       </c>
       <c r="E4" t="n">
-        <v>17.41641</v>
+        <v>16.7193</v>
       </c>
       <c r="F4" t="n">
-        <v>42.80393</v>
+        <v>43.00963</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05102</v>
+        <v>0.05001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81491</v>
+        <v>1.84094</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.01806</v>
+        <v>16.84576</v>
       </c>
       <c r="D6" t="n">
-        <v>16.31369</v>
+        <v>15.9933</v>
       </c>
       <c r="E6" t="n">
-        <v>16.39949</v>
+        <v>16.81128</v>
       </c>
       <c r="F6" t="n">
-        <v>22.38731</v>
+        <v>22.10694</v>
       </c>
       <c r="G6" t="n">
-        <v>34.37679</v>
+        <v>34.64749</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.39487</v>
+        <v>16.59627</v>
       </c>
       <c r="D7" t="n">
-        <v>16.47767</v>
+        <v>16.48115</v>
       </c>
       <c r="E7" t="n">
-        <v>16.73122</v>
+        <v>16.50424</v>
       </c>
       <c r="F7" t="n">
-        <v>22.31853</v>
+        <v>22.28931</v>
       </c>
       <c r="G7" t="n">
-        <v>34.87004</v>
+        <v>34.81973</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.91412</v>
+        <v>16.90193</v>
       </c>
       <c r="D8" t="n">
-        <v>16.31091</v>
+        <v>16.41295</v>
       </c>
       <c r="E8" t="n">
-        <v>16.89488</v>
+        <v>16.49352</v>
       </c>
       <c r="F8" t="n">
-        <v>22.20007</v>
+        <v>22.29298</v>
       </c>
       <c r="G8" t="n">
-        <v>34.52728</v>
+        <v>34.73642</v>
       </c>
     </row>
   </sheetData>
